--- a/01_Growth/Figure_1_source_data.xlsx
+++ b/01_Growth/Figure_1_source_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2237098_ed_ac_uk/Documents/PhD/Thesis/RSC EnvSciNano paper/Github data/01_Growth/Figure_1_Specific_Growth_Rate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2237098_ed_ac_uk/Documents/PhD/Thesis/RSC EnvSciNano paper/Github data/01_Growth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="11_15852447413C9D415FC2E99E2F15072EBC13F74B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93327BE5-9FD6-4083-B887-1B9856FCAC42}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="11_15852447413C9D415FC2E99E2F15072EBC13F74B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B87FA673-3D1C-4343-A104-65D7B04EF04C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
